--- a/wildlife/reports/United-Kingdom/abundance/Abingdon/Flora/abundance.xlsx
+++ b/wildlife/reports/United-Kingdom/abundance/Abingdon/Flora/abundance.xlsx
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D19" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D33" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="34">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D73" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="74">
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D77" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78">

--- a/wildlife/reports/United-Kingdom/abundance/Abingdon/Flora/abundance.xlsx
+++ b/wildlife/reports/United-Kingdom/abundance/Abingdon/Flora/abundance.xlsx
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20">
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D23" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D73" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="74">
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D77" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78">
@@ -1671,10 +1671,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D78" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="79">

--- a/wildlife/reports/United-Kingdom/abundance/Abingdon/Flora/abundance.xlsx
+++ b/wildlife/reports/United-Kingdom/abundance/Abingdon/Flora/abundance.xlsx
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D19" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D33" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="34">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D73" t="n">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74">
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D77" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="78">
@@ -1671,10 +1671,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D78" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="79">

--- a/wildlife/reports/United-Kingdom/abundance/Abingdon/Flora/abundance.xlsx
+++ b/wildlife/reports/United-Kingdom/abundance/Abingdon/Flora/abundance.xlsx
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D19" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20">
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D23" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D33" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="34">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D73" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="74">
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D77" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78">
@@ -1671,10 +1671,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D78" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79">

--- a/wildlife/reports/United-Kingdom/abundance/Abingdon/Flora/abundance.xlsx
+++ b/wildlife/reports/United-Kingdom/abundance/Abingdon/Flora/abundance.xlsx
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D20" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21">
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D25" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D57" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58">
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D65" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="66">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D73" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="74">
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D75" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="76">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D76" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="77">
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D77" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78">

--- a/wildlife/reports/United-Kingdom/abundance/Abingdon/Flora/abundance.xlsx
+++ b/wildlife/reports/United-Kingdom/abundance/Abingdon/Flora/abundance.xlsx
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D73" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="74">
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D77" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="78">
@@ -1671,10 +1671,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D78" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79">
